--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487519_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487519_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. VILLADONIGA AMADO</t>
+          <t>A. HERMIDA PEREZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9445</v>
+        <v>2.899</v>
       </c>
       <c r="E2" t="n">
-        <v>2.3562</v>
+        <v>1.8555</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5881999999999999</v>
+        <v>1.0435</v>
       </c>
       <c r="G2" t="n">
-        <v>3.4691</v>
+        <v>0.2524</v>
       </c>
       <c r="H2" t="n">
-        <v>2.9633</v>
+        <v>1.7169</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5057</v>
+        <v>-1.4646</v>
       </c>
       <c r="J2" t="n">
-        <v>2.4286</v>
+        <v>0.8025</v>
       </c>
       <c r="K2" t="n">
-        <v>2.3477</v>
+        <v>0.1462</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0808</v>
+        <v>0.6563</v>
       </c>
       <c r="M2" t="n">
-        <v>1.0405</v>
+        <v>-0.5502</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6156</v>
+        <v>1.5707</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4249</v>
+        <v>-2.1209</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>0.1958</v>
       </c>
       <c r="Q2" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9792</v>
+        <v>1.1751</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9674</v>
+        <v>-0.3154</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9069</v>
+        <v>-0.6764</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0605</v>
+        <v>0.361</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.492</v>
+        <v>2.7662</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2.7086</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.492</v>
+        <v>0.0576</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. RAMOS DA CONCEIÇAO</t>
+          <t>P. FERNANDEZ GONZALEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9303</v>
+        <v>2.4817</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7049</v>
+        <v>2.2734</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2255</v>
+        <v>0.2083</v>
       </c>
       <c r="G3" t="n">
-        <v>1.268</v>
+        <v>1.5058</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8642</v>
+        <v>2.7935</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5962</v>
+        <v>-1.2877</v>
       </c>
       <c r="J3" t="n">
-        <v>1.7899</v>
+        <v>3.0767</v>
       </c>
       <c r="K3" t="n">
-        <v>2.5433</v>
+        <v>2.38</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.7534</v>
+        <v>0.6967</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5219</v>
+        <v>-1.5709</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6791</v>
+        <v>0.4135</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1572</v>
+        <v>-1.9844</v>
       </c>
       <c r="P3" t="n">
         <v>-0.5875</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9792</v>
+        <v>-1.9585</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3917</v>
+        <v>1.3709</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0332</v>
+        <v>-0.0887</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3435</v>
+        <v>-0.497</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6898</v>
+        <v>0.4083</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2166</v>
+        <v>1.6521</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5507</v>
+        <v>1.6521</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6659</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. HERMIDA PEREZ</t>
+          <t>S. RAMOS DA CONCEIÇAO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5744</v>
+        <v>2.4537</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3438</v>
+        <v>1.6025</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2306</v>
+        <v>0.8512</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2524</v>
+        <v>1.268</v>
       </c>
       <c r="H4" t="n">
-        <v>1.7169</v>
+        <v>1.8642</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.4646</v>
+        <v>-0.5962</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8025</v>
+        <v>1.7899</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1462</v>
+        <v>2.5433</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6563</v>
+        <v>-0.7534</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5502</v>
+        <v>-0.5219</v>
       </c>
       <c r="N4" t="n">
-        <v>1.5707</v>
+        <v>-0.6791</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.1209</v>
+        <v>0.1572</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1958</v>
+        <v>-0.5875</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1751</v>
+        <v>0.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6399</v>
+        <v>0.5567</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.188</v>
+        <v>0.2411</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5481</v>
+        <v>0.3155</v>
       </c>
       <c r="V4" t="n">
-        <v>2.7662</v>
+        <v>1.2166</v>
       </c>
       <c r="W4" t="n">
-        <v>2.7086</v>
+        <v>0.5507</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0576</v>
+        <v>0.6659</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. FERNANDEZ GONZALEZ</t>
+          <t>D. VILLADONIGA AMADO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5737</v>
+        <v>2.1212</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6594</v>
+        <v>1.6399</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0857</v>
+        <v>0.4813</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5058</v>
+        <v>3.4691</v>
       </c>
       <c r="H5" t="n">
-        <v>2.7935</v>
+        <v>2.9633</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.2877</v>
+        <v>0.5057</v>
       </c>
       <c r="J5" t="n">
-        <v>3.0767</v>
+        <v>2.4286</v>
       </c>
       <c r="K5" t="n">
-        <v>2.38</v>
+        <v>2.3477</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6967</v>
+        <v>0.0808</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.5709</v>
+        <v>1.0405</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4135</v>
+        <v>0.6156</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.9844</v>
+        <v>0.4249</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.5875</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9585</v>
+        <v>-0.9792</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3709</v>
+        <v>0.9792</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9967</v>
+        <v>0.1441</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.111</v>
+        <v>0.1906</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1143</v>
+        <v>-0.0465</v>
       </c>
       <c r="V5" t="n">
-        <v>1.6521</v>
+        <v>-1.492</v>
       </c>
       <c r="W5" t="n">
-        <v>1.6521</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3819</v>
+        <v>1.9867</v>
       </c>
       <c r="E6" t="n">
-        <v>1.826</v>
+        <v>2.6447</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4441</v>
+        <v>-0.658</v>
       </c>
       <c r="G6" t="n">
         <v>2.8603</v>
@@ -922,13 +922,13 @@
         <v>0.5875</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.08790000000000001</v>
+        <v>0.517</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8316</v>
+        <v>-0.0129</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7438</v>
+        <v>0.5299</v>
       </c>
       <c r="V6" t="n">
         <v>-0.9988</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7571</v>
+        <v>-0.6235000000000001</v>
       </c>
       <c r="E7" t="n">
         <v>-0.3754</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3817</v>
+        <v>-0.2481</v>
       </c>
       <c r="G7" t="n">
         <v>-0.1575</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5996</v>
+        <v>-0.466</v>
       </c>
       <c r="T7" t="n">
         <v>-0.4158</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1838</v>
+        <v>-0.0501</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. RUANO MARTINEZ</t>
+          <t>A. SYTAR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8486</v>
+        <v>-1.4443</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8294</v>
+        <v>1.3241</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.678</v>
+        <v>-2.7684</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6143</v>
+        <v>0.3966</v>
       </c>
       <c r="H8" t="n">
-        <v>1.9159</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.5302</v>
+        <v>-0.4598</v>
       </c>
       <c r="J8" t="n">
-        <v>2.244</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>1.4357</v>
+        <v>0.7179</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8083</v>
+        <v>-0.0712</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.8583</v>
+        <v>-0.2501</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4802</v>
+        <v>0.1385</v>
       </c>
       <c r="O8" t="n">
-        <v>-3.3385</v>
+        <v>-0.3886</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.1751</v>
+        <v>-1.3709</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.9585</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7834</v>
+        <v>0.5875</v>
       </c>
       <c r="S8" t="n">
-        <v>2.2726</v>
+        <v>1.3549</v>
       </c>
       <c r="T8" t="n">
-        <v>1.6003</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6723</v>
+        <v>0.5439000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.3318</v>
+        <v>-1.8249</v>
       </c>
       <c r="W8" t="n">
-        <v>-1.0564</v>
+        <v>1.8249</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2754</v>
+        <v>-3.6498</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. SYTAR</t>
+          <t>I. SAMA PEREZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8524</v>
+        <v>-1.5803</v>
       </c>
       <c r="E9" t="n">
-        <v>1.8358</v>
+        <v>-0.0646</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.6882</v>
+        <v>-1.5156</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3966</v>
+        <v>-1.3335</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8564000000000001</v>
+        <v>-0.3791</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4598</v>
+        <v>-0.9544</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6467000000000001</v>
+        <v>1.8602</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7179</v>
+        <v>-0.6551</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.0712</v>
+        <v>2.5154</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2501</v>
+        <v>-3.1938</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1385</v>
+        <v>0.276</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3886</v>
+        <v>-3.4698</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.3709</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.9585</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5875</v>
+        <v>1.1751</v>
       </c>
       <c r="S9" t="n">
-        <v>1.9468</v>
+        <v>0.2613</v>
       </c>
       <c r="T9" t="n">
-        <v>1.3227</v>
+        <v>-0.2417</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6241</v>
+        <v>0.503</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.8249</v>
+        <v>0.2754</v>
       </c>
       <c r="W9" t="n">
-        <v>1.8249</v>
+        <v>0.2754</v>
       </c>
       <c r="X9" t="n">
-        <v>-3.6498</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. SAMA PEREZ</t>
+          <t>M. RUANO MARTINEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1859</v>
+        <v>-2.3615</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2693</v>
+        <v>-0.6032999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.9166</v>
+        <v>-1.7582</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.3335</v>
+        <v>-0.6143</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3791</v>
+        <v>1.9159</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9544</v>
+        <v>-2.5302</v>
       </c>
       <c r="J10" t="n">
-        <v>1.8602</v>
+        <v>2.244</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6551</v>
+        <v>1.4357</v>
       </c>
       <c r="L10" t="n">
-        <v>2.5154</v>
+        <v>0.8083</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.1938</v>
+        <v>-2.8583</v>
       </c>
       <c r="N10" t="n">
-        <v>0.276</v>
+        <v>0.4802</v>
       </c>
       <c r="O10" t="n">
-        <v>-3.4698</v>
+        <v>-3.3385</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.7834</v>
+        <v>-1.1751</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.9585</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1751</v>
+        <v>0.7834</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3444</v>
+        <v>0.7597</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4464</v>
+        <v>0.1676</v>
       </c>
       <c r="U10" t="n">
-        <v>0.102</v>
+        <v>0.5921</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2754</v>
+        <v>-1.3318</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2754</v>
+        <v>-1.0564</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5428</v>
+        <v>-2.7149</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.3014</v>
+        <v>-3.6874</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7587</v>
+        <v>0.9725</v>
       </c>
       <c r="G11" t="n">
         <v>-3.6688</v>
@@ -1312,13 +1312,13 @@
         <v>0.7834</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5814</v>
+        <v>0.2464</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3982</v>
+        <v>0.2158</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1833</v>
+        <v>0.0306</v>
       </c>
       <c r="V11" t="n">
         <v>1.8825</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.218</v>
+        <v>3.2178</v>
       </c>
       <c r="E12" t="n">
-        <v>6.6094</v>
+        <v>6.609400000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.3913</v>
+        <v>-3.391500000000001</v>
       </c>
       <c r="G12" t="n">
         <v>3.9781</v>
@@ -1390,13 +1390,13 @@
         <v>7.8338</v>
       </c>
       <c r="S12" t="n">
-        <v>2.9701</v>
+        <v>2.97</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2176</v>
+        <v>-0.2177</v>
       </c>
       <c r="U12" t="n">
-        <v>3.1878</v>
+        <v>3.1877</v>
       </c>
       <c r="V12" t="n">
         <v>2.1453</v>
@@ -1405,13 +1405,13 @@
         <v>6.448399999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>-4.303199999999999</v>
+        <v>-4.3032</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>K. VAN WIJK</t>
+          <t>M. PAZ CACHEIRO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,40 +1423,40 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.8333</v>
+        <v>2.7232</v>
       </c>
       <c r="E13" t="n">
-        <v>5.0097</v>
+        <v>3.7539</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.1764</v>
+        <v>-1.0307</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.0409</v>
+        <v>2.8157</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.425</v>
+        <v>-0.3923</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3841</v>
+        <v>3.208</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5142</v>
+        <v>4.5042</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.0668</v>
+        <v>1.3066</v>
       </c>
       <c r="L13" t="n">
-        <v>1.581</v>
+        <v>3.1976</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.5551</v>
+        <v>-1.6884</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.3582</v>
+        <v>-1.6988</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.1969</v>
+        <v>0.0104</v>
       </c>
       <c r="P13" t="n">
         <v>0.3917</v>
@@ -1468,28 +1468,28 @@
         <v>1.3709</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5573</v>
+        <v>-0.5417999999999999</v>
       </c>
       <c r="T13" t="n">
+        <v>-0.3794</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-0.1625</v>
+      </c>
+      <c r="V13" t="n">
         <v>0.0576</v>
       </c>
-      <c r="U13" t="n">
-        <v>0.4997</v>
-      </c>
-      <c r="V13" t="n">
-        <v>3.9252</v>
-      </c>
       <c r="W13" t="n">
-        <v>5.4171</v>
+        <v>0.6083</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.492</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. PAZ CACHEIRO</t>
+          <t>K. VAN WIJK</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,40 +1501,40 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.0779</v>
+        <v>2.3466</v>
       </c>
       <c r="E14" t="n">
-        <v>3.2422</v>
+        <v>4.6004</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.1643</v>
+        <v>-2.2538</v>
       </c>
       <c r="G14" t="n">
-        <v>2.8157</v>
+        <v>-2.0409</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.3923</v>
+        <v>-2.425</v>
       </c>
       <c r="I14" t="n">
-        <v>3.208</v>
+        <v>0.3841</v>
       </c>
       <c r="J14" t="n">
-        <v>4.5042</v>
+        <v>0.5142</v>
       </c>
       <c r="K14" t="n">
-        <v>1.3066</v>
+        <v>-1.0668</v>
       </c>
       <c r="L14" t="n">
-        <v>3.1976</v>
+        <v>1.581</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.6884</v>
+        <v>-2.5551</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.6988</v>
+        <v>-1.3582</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0104</v>
+        <v>-1.1969</v>
       </c>
       <c r="P14" t="n">
         <v>0.3917</v>
@@ -1546,22 +1546,22 @@
         <v>1.3709</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.1872</v>
+        <v>0.0706</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.891</v>
+        <v>-0.3517</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2961</v>
+        <v>0.4223</v>
       </c>
       <c r="V14" t="n">
-        <v>0.0576</v>
+        <v>3.9252</v>
       </c>
       <c r="W14" t="n">
-        <v>0.6083</v>
+        <v>5.4171</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.5507</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4343</v>
+        <v>1.5901</v>
       </c>
       <c r="E15" t="n">
-        <v>1.1935</v>
+        <v>1.2958</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2408</v>
+        <v>0.2943</v>
       </c>
       <c r="G15" t="n">
         <v>1.731</v>
@@ -1624,13 +1624,13 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2967</v>
+        <v>-0.1409</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0594</v>
+        <v>0.0429</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2373</v>
+        <v>-0.1838</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2476</v>
+        <v>1.1489</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1327</v>
+        <v>0.4163</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1149</v>
+        <v>0.7325</v>
       </c>
       <c r="G16" t="n">
         <v>-1.361</v>
@@ -1702,13 +1702,13 @@
         <v>2.546</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.328</v>
+        <v>-0.4267</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2823</v>
+        <v>-0.4341</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6102</v>
+        <v>0.0074</v>
       </c>
       <c r="V16" t="n">
         <v>0.3905</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2935</v>
+        <v>0.8744</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5276</v>
+        <v>0.291</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8212</v>
+        <v>0.5834</v>
       </c>
       <c r="G17" t="n">
         <v>0.6312</v>
@@ -1780,13 +1780,13 @@
         <v>1.7626</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1211</v>
+        <v>-0.5402</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.7227</v>
+        <v>-0.904</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6016</v>
+        <v>0.3638</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1484</v>
+        <v>-0.681</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7329</v>
+        <v>1.0399</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.8813</v>
+        <v>-1.7209</v>
       </c>
       <c r="G19" t="n">
         <v>-1.3634</v>
@@ -1936,13 +1936,13 @@
         <v>1.1751</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7423</v>
+        <v>-0.275</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8734</v>
+        <v>-0.5664</v>
       </c>
       <c r="U19" t="n">
-        <v>0.131</v>
+        <v>0.2914</v>
       </c>
       <c r="V19" t="n">
         <v>-0.2178</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1066</v>
+        <v>-1.6494</v>
       </c>
       <c r="E20" t="n">
         <v>-0.7224</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3842</v>
+        <v>-0.927</v>
       </c>
       <c r="G20" t="n">
         <v>-1.9969</v>
@@ -2014,13 +2014,13 @@
         <v>1.1751</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0095</v>
+        <v>-0.5523</v>
       </c>
       <c r="T20" t="n">
         <v>-0.1317</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8777</v>
+        <v>-0.4205</v>
       </c>
       <c r="V20" t="n">
         <v>-0.2754</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1929</v>
+        <v>-1.8905</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9642</v>
+        <v>-1.5548</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2288</v>
+        <v>-0.3357</v>
       </c>
       <c r="G21" t="n">
         <v>-0.6306</v>
@@ -2092,13 +2092,13 @@
         <v>0.9792</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.166</v>
+        <v>0.1364</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7128</v>
+        <v>-0.3035</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5469000000000001</v>
+        <v>0.4399</v>
       </c>
       <c r="V21" t="n">
         <v>-2.3756</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.5908</v>
+        <v>-2.4083</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4205</v>
+        <v>-2.3182</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1703</v>
+        <v>-0.0901</v>
       </c>
       <c r="G22" t="n">
         <v>0.4347</v>
@@ -2170,13 +2170,13 @@
         <v>0.9792</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2018</v>
+        <v>-0.0193</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2794</v>
+        <v>-0.177</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0776</v>
+        <v>0.1578</v>
       </c>
       <c r="V22" t="n">
         <v>-2.8237</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.1062</v>
+        <v>-4.63</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.3252</v>
+        <v>-3.4509</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.781</v>
+        <v>-1.1792</v>
       </c>
       <c r="G23" t="n">
         <v>-2.3748</v>
@@ -2248,13 +2248,13 @@
         <v>2.3502</v>
       </c>
       <c r="S23" t="n">
-        <v>1.6615</v>
+        <v>0.1376</v>
       </c>
       <c r="T23" t="n">
-        <v>1.1427</v>
+        <v>0.017</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5187</v>
+        <v>0.1206</v>
       </c>
       <c r="V23" t="n">
         <v>-0.8260999999999999</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.2179</v>
+        <v>-2.5356</v>
       </c>
       <c r="E24" t="n">
-        <v>3.391499999999999</v>
+        <v>3.391399999999997</v>
       </c>
       <c r="F24" t="n">
-        <v>-6.609399999999999</v>
+        <v>-5.927199999999999</v>
       </c>
       <c r="G24" t="n">
         <v>-3.9781</v>
@@ -2326,13 +2326,13 @@
         <v>13.7092</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.9702</v>
+        <v>-2.288</v>
       </c>
       <c r="T24" t="n">
-        <v>-3.1878</v>
+        <v>-3.1879</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2178000000000002</v>
+        <v>0.9000000000000001</v>
       </c>
       <c r="V24" t="n">
         <v>-2.1453</v>
